--- a/docs/perechen-otchetov/obrazcy/ФО-53.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-53.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-53" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-53'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +30,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +91,27 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,44 +145,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,262 +592,704 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="7.8" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-53</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>за период с 01.09.2026 по 30.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Курсовая разница по основному долгу</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.09.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Остаток основного долга, в валюте</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Курс, сом за единицу</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Остаток в сомах</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Курсовая разница за период</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>на начало периода</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>освоено</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>выдано</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>погашено</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>списано</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>курсовая разница</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>на конец периода</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>на начало</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>на конец</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>на начало периода</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>движение за период</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>на конец периода</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="n">
-        <v>5232000</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>-437000</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>4812500</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="n">
-        <v>5232000</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>-437000</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>4812500</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>35688</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>437</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>35367.5</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>USD — доллар США</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>23544</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>437</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>23187.5</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,20000 → 87,50000)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="14" t="n">
+        <v>270</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="14" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>10464</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>№ 19-3/061 от 11.04.2019, USD</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="21" t="n">
+        <v>10464</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,20000 → 87,50000)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>7848</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>7875</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>№ 20-5/118 от 23.06.2020, USD</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="21" t="n">
+        <v>7848</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>7875</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,20000 → 87,50000)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>ОсОО «Кут-Мүлк»</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="8" t="n">
-        <v>5232000</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>-437000</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>4812500</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>№ 23-1/019 от 05.05.2023</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>5232000</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>-437000</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>4812500</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>17500</v>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>5232</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>437</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>4812.5</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>№ 23-1/019 от 05.05.2023, USD</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="21" t="n">
+        <v>5232</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>437</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>4812.5</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,20000 → 87,50000)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="14" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>EUR — евро</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>12144</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>12180</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,20000 → 101,50000)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Арча Энерго»</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>7286.4</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>7308</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="21" t="n">
+        <v>7286.4</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>7308</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,20000 → 101,50000)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>4857.6</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>№ 21-1/207 от 15.11.2021, EUR</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="21" t="n">
+        <v>4857.6</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,20000 → 101,50000)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="14" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="I4:K4"/>
+  <mergeCells count="6">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-53 · сформировал Бекова Н. С. 06.10.2026 12:00 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -757,7 +1299,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>ФО-53 «Курсовая разница по основному долгу за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>01.09.2026 – 30.09.2026 (по умолчанию — прошлый месяц)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Валюта</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>все иностранные: USD, EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Валюта → Заёмщик → кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Реквизиты разрезов</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>на 30.09.2026 — последний день периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>на начало периода — на 31.08.2026: USD 87,20000, EUR 101,20000; на конец — на 30.09.2026: USD 87,50000, EUR 101,50000; выдача, погашение и списание — по курсу дня операции (погашение 05.09.2026 — USD 87,40000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Курсовая разница</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>переоценка остатка основного долга при каждой смене курса: остаток на конец предыдущего дня × (новый курс − прежний), за период — сумма по дням периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -766,474 +1490,489 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ФО-53 «Расчёт в валюте и курсовая разница за период» — карточка</t>
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>ФО-53 «Курсовая разница по основному долгу за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>ФО-53</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Курсовая разница по основному долгу за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Расчёты</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶740</t>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶740; ТЗ 18; старая система</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Бухгалтерии и департаментам — расчёт по кредитам в иностранной валюте и курсовая разница за период.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Бухгалтерии — сколько за период дала курсовая разница по основному долгу кредитов в иностранной валюте: остаток на начало и на конец в сомах и в валюте договора, выдано, погашено, списано и переоценка остатка при смене курса — по каждому кредиту и итогом по валютам. Нужна для переоценки валютных кредитов в учёте после закрытия месяца; департаменты, ведущие валютные кредиты, формируют её отбором своего департамента. Курсовую разницу по процентам и штрафам показывает ФО-07 — колонкой в ведомости по процентам и штрафам, здесь она не повторяется; остаток на одну дату в валюте договора — ФО-02, платежи в сомах, как поступили, — ФО-04. Прежнее название — «Расчёт в валюте и курсовая разница за период» (оф. ТЗ: «по кредитам в иностранной валюте доступны расчеты в валюте и расчет курсовой разницы на заданный период времени»); в старой системе отдельного отчёта не было — была колонка «Курсовая разница» у кредита в отчёте по задолженности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>За период (по умолчанию — прошлый месяц); по требованию.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>За период: ежемесячно после закрытия месяца и по требованию; по умолчанию — прошлый месяц. Можно выбрать любой период (за год — с 1 января, за всё время — с даты выдачи). Отчёт за закрытый период не меняется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>• Период — прошлый месяц
-• Валюта — все иностранные
-• Подразделение — все
-• Единица — сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>• Период — прошлый месяц; можно выбрать любой
+• Единица — тыс. сом (можно выбрать «сом»)
+• Валюта — все иностранные; можно выбрать одну
+• Разрезы — до шести уровней в любом порядке; по умолчанию валюта → заёмщик → кредит. Доступны: валюта, департамент, отдел, куратор, кредитная программа, вид кредита, источник финансирования, кредитная линия, область, район, отрасль, группа платёжеспособности, заёмщик
+• Отбор — по любому из разрезов</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="315" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Валюта → заёмщик → кредит. Подытоги на каждом уровне, сверху ИТОГО. Колонки в валюте не суммируются между валютами: на уровне ИТОГО заполнены только колонки в сомах.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Строка детали — кредит в иностранной валюте: основной долг на начало периода, выдано, погашено, списано, курсовая разница, на конец периода; на конец = на начало + выдано − погашено − списано + курсовая разница. В отчёт попадает кредит в иностранной валюте, у которого есть остаток основного долга на начало или на конец периода либо движение основного долга внутри периода: погашенный или списанный в периоде — со своим движением и нулём на конец. Кредиты в сомах в отчёт не попадают: курсовой разницы у них нет. Над кредитами разрезы, по умолчанию валюта → заёмщик; строка заёмщика есть всегда, даже при одном кредите. Реквизиты разрезов (заёмщик, подразделение, куратор, группа) — на последний день периода. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: валюты — по справочнику валют (USD, EUR, …); заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора. Суммы — в тыс. сом: на начало — по курсу на день перед началом периода, выдано, погашено и списано — по курсу дня операции, на конец — по курсу последнего дня периода. Курсовая разница — показатель расчёта задолженности (переоценка остатка основного долга нарастающим итогом), за период — разность на конец периода и на день перед его началом; отчёт её не досчитывает, а сверяет: ненулевая разница «на конец − на начало − выдано + погашено + списано − курсовая разница» помечается у кредита «не сходится с потоками». Нет курса на нужную дату — суммы в сомах и курсовая разница кредита пусты, в наименовании пометка «нет курса на ДД.ММ.ГГГГ», под датой ⚠. Под валютным кредитом курсивом строка «в тыс. &lt;валюта&gt; (курс на начало → на конец)» — тот же основной долг в валюте договора, без курсовой разницы; такая же строка стоит под строкой валюты — группа однородна, суммы в валюте в ней складываются; в итоги эти строки не входят. Печать — A4 альбомная в одну страницу по ширине.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>по умолчанию: Валюта → Заёмщик → кредит; можно выбрать: Валюта, Департамент, Отдел, Куратор, Кредитная программа, Вид кредита, Источник финансирования, Кредитная линия, Область, Район, Отрасль, Группа платёжеспособности, Заёмщик</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Кредитов в иностранной валюте с остатком или движением основного долга за период по условиям отбора нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Расчёт в валюте и курсовая разница за период»; в старой системе отдельного отчёта не было — колонка «Курсовая разница» у кредита в отчёте по задолженности. Строка — кредит в иностранной валюте под валютой и заёмщиком: основной долг на начало, выдано, погашено, списано, курсовая разница и на конец — в сомах, под кредитом и под валютой — то же в валюте договора. Курсовая разница по процентам и штрафам — в ФО-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>валюта, заёмщик или номер договора</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>валюта кредита</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr"/>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>валюта, заёмщик или кредит «№ … от …, USD» — по уровню строки; под кредитом и под валютой — строка «в тыс. &lt;валюта&gt; (курс на начало → на конец)» с теми же суммами в валюте договора</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr"/>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>число заёмщиков с кредитами в иностранной валюте; у заёмщика и кредита пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr"/>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>число кредитов в иностранной валюте; у кредита пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>на начало периода</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Остаток основного долга, в валюте</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>остаток на начало периода</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>освоено</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Остаток основного долга, в валюте</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>освоение в периоде</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>остаток основного долга на конец дня перед началом периода, в сомах по курсу того дня; = ФО-02 «по основной сумме» на первый день периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>выдано</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>освоено (перечислено) за период; каждая выдача в сомах по курсу дня выдачи</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>погашено</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Остаток основного долга, в валюте</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>погашение основной суммы в периоде</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>часть поступлений, разнесённая на основной долг; в сомах, как поступили (по курсу дня платежа); = ФО-04 «по основной сумме»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>списано</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>основной долг, снятый решением о списании; в сомах по курсу дня решения; = ФО-11 «по основной сумме»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>курсовая разница</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>переоценка остатка основного долга при смене курса за период: при каждой смене курса — остаток на конец предыдущего дня × (новый курс − прежний); «+» — долг в сомах вырос, «−» — уменьшился; = на конец − на начало − выдано + погашено + списано</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>на конец периода</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Остаток основного долга, в валюте</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>остаток на конец периода</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>на начало</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Курс, сом за единицу</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>официальный курс на дату начала периода</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>на конец</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Курс, сом за единицу</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>официальный курс на дату окончания периода</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>на начало периода</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Остаток в сомах</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>остаток на начало × курс на начало</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>движение за период</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Остаток в сомах</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>освоено минус погашено, каждая операция по курсу на дату операции</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>на конец периода</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Остаток в сомах</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>остаток на конец × курс на конец</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Курсовая разница за период</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>остаток в сомах на конец − (на начало + движение за период); плюс — прирост долга в сомах</t>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>Основной долг</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>остаток основного долга на конец последнего дня периода, в сомах по курсу этого дня; = ФО-02 «по основной сумме» на следующий день</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026 по набору: заёмщиков 5, кредитов 5 (USD — КЗ-11, КЗ-21 № 19-3/061, КЗ-23; EUR — КЗ-22, КЗ-25). ИТОГО: на начало 35 688,000 + выдано 0,000 − погашено 437,000 − списано 0,000 + курсовая разница 116,500 = на конец 35 367,500 тыс. сом. По валютам: USD — 23 544,000 − 437,000 + 80,500 = 23 187,500 (270,000 → 265,000 тыс. USD); EUR — 12 144,000 + 36,000 = 12 180,000 (120,000 тыс. EUR на обоих концах).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.</t>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>В каждой строке на конец = на начало + выдано − погашено − списано + курсовая разница; строка разреза = сумма строк на уровень ниже по каждой сумме и по «Кредитов»; строки «в тыс. USD/EUR» в итоги не входят; строка «в тыс. USD» под строкой валюты = сумма таких строк её кредитов.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>Курсовая разница ИТОГО 116,500 = курсовой разнице в изменении остатка ФО-24 за сентябрь 2026: КЗ-11 17,500, КЗ-21 36,000, КЗ-22 14,400, КЗ-23 27,000, КЗ-25 21,600.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>КЗ-11 № 23-1/019: на 31.08.2026 — 60,000 тыс. USD × 87,20 = 5 232,000; погашение 05.09.2026 (п/п 4372) — 5,000 тыс. USD основной суммы = 437,000 тыс. сом по курсу 87,40 (= ФО-04); на 30.09.2026 — 55,000 тыс. USD × 87,50 = 4 812,500; курсовая разница по сменам курса: 60 000 × (87,40 − 87,20) + 55 000 × (87,50 − 87,40) = 12 000 + 5 500 = 17 500,00 сом = 4 812,500 − 5 232,000 + 437,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>На конец по кредиту = ФО-02 «по основной сумме» на 01.10.2026: КЗ-11 4 812,500, КЗ-21 № 19-3/061 10 500,000, КЗ-22 4 872,000, КЗ-23 7 875,000; КЗ-25 7 308,000 (= ФО-24, ФО-25, ФО-28; в образце ФО-02 его нет). На начало = ФО-24 «на начало» по заёмщику: КЗ-11 5 232,000, КЗ-22 4 857,600, КЗ-23 7 848,000, КЗ-25 7 286,400; у КЗ-21 — только кредит № 19-3/061: 10 464,000 из 15 464,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>Не попадают кредиты в сомах — в том числе два кредита КЗ-21 (№ 22-3/014 и № 24-3/105): у ФО-24 они входят в остаток заёмщика, курсовой разницы у них нет. Выдач и списаний по валютным кредитам в сентябре нет — «выдано» и «списано» 0,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Отбор «Департамент регионального развития»: 1 заёмщик, 1 кредит (КЗ-23), 7 848,000 + 27,000 = 7 875,000; под заголовком строка «Отбор: Департамент регионального развития».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/perechen-otchetov/obrazcy/ФО-53.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-53.xlsx
@@ -1912,7 +1912,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="75" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="27" t="inlineStr">
         <is>
           <t>5.</t>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>На конец по кредиту = ФО-02 «по основной сумме» на 01.10.2026: КЗ-11 4 812,500, КЗ-21 № 19-3/061 10 500,000, КЗ-22 4 872,000, КЗ-23 7 875,000; КЗ-25 7 308,000 (= ФО-24, ФО-25, ФО-28; в образце ФО-02 его нет). На начало = ФО-24 «на начало» по заёмщику: КЗ-11 5 232,000, КЗ-22 4 857,600, КЗ-23 7 848,000, КЗ-25 7 286,400; у КЗ-21 — только кредит № 19-3/061: 10 464,000 из 15 464,000.</t>
+          <t>На конец по кредиту = ФО-02 «по основной сумме» на 01.10.2026: КЗ-11 4 812,500, КЗ-21 № 19-3/061 10 500,000, КЗ-22 4 872,000, КЗ-23 7 875,000; КЗ-25 7 308,000 (= ФО-02, ФО-24, ФО-25, ФО-28). На начало = ФО-24 «на начало» по заёмщику: КЗ-11 5 232,000, КЗ-22 4 857,600, КЗ-23 7 848,000, КЗ-25 7 286,400; у КЗ-21 — только кредит № 19-3/061: 10 464,000 из 15 464,000.</t>
         </is>
       </c>
     </row>
